--- a/data.mn/public/datasets/livestock-total.xlsx
+++ b/data.mn/public/datasets/livestock-total.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,1042 +414,948 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>type_of_livestock</t>
+          <t>year</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>Total — Total</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B2" t="n">
+        <v>22574.72</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B3" t="n">
+        <v>22692.57</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B4" t="n">
+        <v>23108.06</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B5" t="n">
+        <v>23538.01</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B6" t="n">
+        <v>24313.47</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B7" t="n">
+        <v>24351.58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B8" t="n">
+        <v>23683.96</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B9" t="n">
+        <v>22942.12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B10" t="n">
+        <v>24025.67</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B11" t="n">
+        <v>24201.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B12" t="n">
+        <v>23771.48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B13" t="n">
+        <v>24263.07</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B14" t="n">
+        <v>24764.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B15" t="n">
+        <v>23570.32</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B16" t="n">
+        <v>22591.93</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B17" t="n">
+        <v>22485.49</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B18" t="n">
+        <v>22590.51</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B19" t="n">
+        <v>22741.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B20" t="n">
+        <v>23122.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B21" t="n">
+        <v>24674.93</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B22" t="n">
+        <v>25856.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B23" t="n">
+        <v>25527.91</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B24" t="n">
+        <v>25694.09</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B25" t="n">
+        <v>24688.34</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B26" t="n">
+        <v>26778.42</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B27" t="n">
+        <v>28572.34</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B28" t="n">
+        <v>29300.14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B29" t="n">
+        <v>31292.32</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B30" t="n">
+        <v>32897.54</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B31" t="n">
+        <v>33568.9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30227.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B33" t="n">
+        <v>26075.35</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B34" t="n">
+        <v>23897.58</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B35" t="n">
+        <v>25427.71</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B36" t="n">
+        <v>28027.96</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B37" t="n">
+        <v>30398.84</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B38" t="n">
+        <v>34802.95</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B39" t="n">
+        <v>40263.86</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B40" t="n">
+        <v>43288.53</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B41" t="n">
+        <v>43981.02</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B42" t="n">
+        <v>32729.52</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B43" t="n">
+        <v>36335.8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B44" t="n">
+        <v>40920.92</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B45" t="n">
+        <v>45144.32</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B46" t="n">
+        <v>51982.58</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B47" t="n">
+        <v>55979.78</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B48" t="n">
+        <v>61549.24</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B49" t="n">
+        <v>66218.96000000001</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B50" t="n">
+        <v>66460.17999999999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B51" t="n">
+        <v>70969.32000000001</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B52" t="n">
+        <v>67068.49000000001</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B53" t="n">
+        <v>67343.75999999999</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B54" t="n">
+        <v>71121.45</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B55" t="n">
+        <v>64681.88</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57649.66</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58104.21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>он</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>Бүгд — Улсын дүн</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="A2" t="n">
         <v>1970</v>
       </c>
-      <c r="D2" t="n">
+      <c r="B2" t="n">
         <v>22574.72</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="A3" t="n">
         <v>1971</v>
       </c>
-      <c r="D3" t="n">
+      <c r="B3" t="n">
         <v>22692.57</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="A4" t="n">
         <v>1972</v>
       </c>
-      <c r="D4" t="n">
+      <c r="B4" t="n">
         <v>23108.06</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="A5" t="n">
         <v>1973</v>
       </c>
-      <c r="D5" t="n">
+      <c r="B5" t="n">
         <v>23538.01</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="A6" t="n">
         <v>1974</v>
       </c>
-      <c r="D6" t="n">
+      <c r="B6" t="n">
         <v>24313.47</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="A7" t="n">
         <v>1975</v>
       </c>
-      <c r="D7" t="n">
+      <c r="B7" t="n">
         <v>24351.58</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+      <c r="A8" t="n">
         <v>1976</v>
       </c>
-      <c r="D8" t="n">
+      <c r="B8" t="n">
         <v>23683.96</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+      <c r="A9" t="n">
         <v>1977</v>
       </c>
-      <c r="D9" t="n">
+      <c r="B9" t="n">
         <v>22942.12</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+      <c r="A10" t="n">
         <v>1978</v>
       </c>
-      <c r="D10" t="n">
+      <c r="B10" t="n">
         <v>24025.67</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="A11" t="n">
         <v>1979</v>
       </c>
-      <c r="D11" t="n">
+      <c r="B11" t="n">
         <v>24201.2</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+      <c r="A12" t="n">
         <v>1980</v>
       </c>
-      <c r="D12" t="n">
+      <c r="B12" t="n">
         <v>23771.48</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+      <c r="A13" t="n">
         <v>1981</v>
       </c>
-      <c r="D13" t="n">
+      <c r="B13" t="n">
         <v>24263.07</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+      <c r="A14" t="n">
         <v>1982</v>
       </c>
-      <c r="D14" t="n">
+      <c r="B14" t="n">
         <v>24764.65</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="A15" t="n">
         <v>1983</v>
       </c>
-      <c r="D15" t="n">
+      <c r="B15" t="n">
         <v>23570.32</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+      <c r="A16" t="n">
         <v>1984</v>
       </c>
-      <c r="D16" t="n">
+      <c r="B16" t="n">
         <v>22591.93</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="A17" t="n">
         <v>1985</v>
       </c>
-      <c r="D17" t="n">
+      <c r="B17" t="n">
         <v>22485.49</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+      <c r="A18" t="n">
         <v>1986</v>
       </c>
-      <c r="D18" t="n">
+      <c r="B18" t="n">
         <v>22590.51</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
+      <c r="A19" t="n">
         <v>1987</v>
       </c>
-      <c r="D19" t="n">
+      <c r="B19" t="n">
         <v>22741.1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+      <c r="A20" t="n">
         <v>1988</v>
       </c>
-      <c r="D20" t="n">
+      <c r="B20" t="n">
         <v>23122.25</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
+      <c r="A21" t="n">
         <v>1989</v>
       </c>
-      <c r="D21" t="n">
+      <c r="B21" t="n">
         <v>24674.93</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
+      <c r="A22" t="n">
         <v>1990</v>
       </c>
-      <c r="D22" t="n">
+      <c r="B22" t="n">
         <v>25856.9</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
+      <c r="A23" t="n">
         <v>1991</v>
       </c>
-      <c r="D23" t="n">
+      <c r="B23" t="n">
         <v>25527.91</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
+      <c r="A24" t="n">
         <v>1992</v>
       </c>
-      <c r="D24" t="n">
+      <c r="B24" t="n">
         <v>25694.09</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
+      <c r="A25" t="n">
         <v>1993</v>
       </c>
-      <c r="D25" t="n">
+      <c r="B25" t="n">
         <v>24688.34</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
+      <c r="A26" t="n">
         <v>1994</v>
       </c>
-      <c r="D26" t="n">
+      <c r="B26" t="n">
         <v>26778.42</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
+      <c r="A27" t="n">
         <v>1995</v>
       </c>
-      <c r="D27" t="n">
+      <c r="B27" t="n">
         <v>28572.34</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
+      <c r="A28" t="n">
         <v>1996</v>
       </c>
-      <c r="D28" t="n">
+      <c r="B28" t="n">
         <v>29300.14</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
+      <c r="A29" t="n">
         <v>1997</v>
       </c>
-      <c r="D29" t="n">
+      <c r="B29" t="n">
         <v>31292.32</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
+      <c r="A30" t="n">
         <v>1998</v>
       </c>
-      <c r="D30" t="n">
+      <c r="B30" t="n">
         <v>32897.54</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
+      <c r="A31" t="n">
         <v>1999</v>
       </c>
-      <c r="D31" t="n">
+      <c r="B31" t="n">
         <v>33568.9</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
+      <c r="A32" t="n">
         <v>2000</v>
       </c>
-      <c r="D32" t="n">
+      <c r="B32" t="n">
         <v>30227.5</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
+      <c r="A33" t="n">
         <v>2001</v>
       </c>
-      <c r="D33" t="n">
+      <c r="B33" t="n">
         <v>26075.35</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
+      <c r="A34" t="n">
         <v>2002</v>
       </c>
-      <c r="D34" t="n">
+      <c r="B34" t="n">
         <v>23897.58</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
+      <c r="A35" t="n">
         <v>2003</v>
       </c>
-      <c r="D35" t="n">
+      <c r="B35" t="n">
         <v>25427.71</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
+      <c r="A36" t="n">
         <v>2004</v>
       </c>
-      <c r="D36" t="n">
+      <c r="B36" t="n">
         <v>28027.96</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
+      <c r="A37" t="n">
         <v>2005</v>
       </c>
-      <c r="D37" t="n">
+      <c r="B37" t="n">
         <v>30398.84</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
+      <c r="A38" t="n">
         <v>2006</v>
       </c>
-      <c r="D38" t="n">
+      <c r="B38" t="n">
         <v>34802.95</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
+      <c r="A39" t="n">
         <v>2007</v>
       </c>
-      <c r="D39" t="n">
+      <c r="B39" t="n">
         <v>40263.86</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
+      <c r="A40" t="n">
         <v>2008</v>
       </c>
-      <c r="D40" t="n">
+      <c r="B40" t="n">
         <v>43288.53</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
+      <c r="A41" t="n">
         <v>2009</v>
       </c>
-      <c r="D41" t="n">
+      <c r="B41" t="n">
         <v>43981.02</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
+      <c r="A42" t="n">
         <v>2010</v>
       </c>
-      <c r="D42" t="n">
+      <c r="B42" t="n">
         <v>32729.52</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
+      <c r="A43" t="n">
         <v>2011</v>
       </c>
-      <c r="D43" t="n">
+      <c r="B43" t="n">
         <v>36335.8</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
+      <c r="A44" t="n">
         <v>2012</v>
       </c>
-      <c r="D44" t="n">
+      <c r="B44" t="n">
         <v>40920.92</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
+      <c r="A45" t="n">
         <v>2013</v>
       </c>
-      <c r="D45" t="n">
+      <c r="B45" t="n">
         <v>45144.32</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
+      <c r="A46" t="n">
         <v>2014</v>
       </c>
-      <c r="D46" t="n">
+      <c r="B46" t="n">
         <v>51982.58</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
+      <c r="A47" t="n">
         <v>2015</v>
       </c>
-      <c r="D47" t="n">
+      <c r="B47" t="n">
         <v>55979.78</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
+      <c r="A48" t="n">
         <v>2016</v>
       </c>
-      <c r="D48" t="n">
+      <c r="B48" t="n">
         <v>61549.24</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
+      <c r="A49" t="n">
         <v>2017</v>
       </c>
-      <c r="D49" t="n">
+      <c r="B49" t="n">
         <v>66218.96000000001</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
+      <c r="A50" t="n">
         <v>2018</v>
       </c>
-      <c r="D50" t="n">
+      <c r="B50" t="n">
         <v>66460.17999999999</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
+      <c r="A51" t="n">
         <v>2019</v>
       </c>
-      <c r="D51" t="n">
+      <c r="B51" t="n">
         <v>70969.32000000001</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
+      <c r="A52" t="n">
         <v>2020</v>
       </c>
-      <c r="D52" t="n">
+      <c r="B52" t="n">
         <v>67068.49000000001</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
+      <c r="A53" t="n">
         <v>2021</v>
       </c>
-      <c r="D53" t="n">
+      <c r="B53" t="n">
         <v>67343.75999999999</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
+      <c r="A54" t="n">
         <v>2022</v>
       </c>
-      <c r="D54" t="n">
+      <c r="B54" t="n">
         <v>71121.45</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
+      <c r="A55" t="n">
         <v>2023</v>
       </c>
-      <c r="D55" t="n">
+      <c r="B55" t="n">
         <v>64681.88</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
+      <c r="A56" t="n">
         <v>2024</v>
       </c>
-      <c r="D56" t="n">
+      <c r="B56" t="n">
         <v>57649.66</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
+      <c r="A57" t="n">
         <v>2025</v>
       </c>
-      <c r="D57" t="n">
+      <c r="B57" t="n">
         <v>58104.21</v>
       </c>
     </row>
